--- a/DataTables/DetailText/剧情/009知州有请.xlsx
+++ b/DataTables/DetailText/剧情/009知州有请.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B4B6FFB-1CF1-4E57-BA95-E4F55734FF66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82DF50F6-39F3-40E9-9E75-DADF4786029E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -471,14 +471,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>res://Assets/Background/010/010_01.png</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>res://Assets/Background/010/010_02.png</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <r>
       <t>一会儿</t>
     </r>
@@ -961,6 +953,118 @@
   </si>
   <si>
     <t>008_02</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>res://Assets/Background/0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>09</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>/0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>09</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>_01.png</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>res://Assets/Background/0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>09</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>/0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>09</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>_0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>.png</t>
+    </r>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1510,7 +1614,7 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>47</v>
@@ -1529,7 +1633,7 @@
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="17" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -1715,7 +1819,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="8"/>
       <c r="G4" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>36</v>
@@ -1738,7 +1842,7 @@
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
@@ -1758,7 +1862,7 @@
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -1780,7 +1884,7 @@
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
@@ -1799,7 +1903,7 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="2" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="H8" s="19" t="s">
         <v>40</v>
@@ -1824,7 +1928,7 @@
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="20" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
@@ -1846,7 +1950,7 @@
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
@@ -1868,7 +1972,7 @@
         <v>29</v>
       </c>
       <c r="H11" s="19" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -1888,7 +1992,7 @@
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">

--- a/DataTables/DetailText/剧情/009知州有请.xlsx
+++ b/DataTables/DetailText/剧情/009知州有请.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82DF50F6-39F3-40E9-9E75-DADF4786029E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61BD7E42-AF12-47C1-8C54-5975ED13382A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -360,6 +360,137 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t>陈皮，跟我去后院收拾收拾库房，一会儿药材就要送来了，得赶紧腾出地方。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>陈皮</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>知州有请</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>好</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>嘞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>浙江省淳安建德两</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>县</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>突发水灾，周边各地已有瘟疫出现，朝廷为防止疫情扩散，特令周边州府发放赈灾药材。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>好的好的。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>朝廷</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>调拨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>了</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>赈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>灾</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>药</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>材，</t>
+    </r>
     <r>
       <rPr>
         <sz val="11"/>
@@ -378,6 +509,506 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
+      <t>次不光惠民</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>药</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>局，咱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>们这</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>些医</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>馆药铺</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>也要一起帮忙</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>发</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>放。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei UI"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>09</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>008_02</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>res://Assets/Background/0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>09</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>/0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>09</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>_01.png</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>res://Assets/Background/0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>09</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>/0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>09</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>_0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>.png</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>昨日，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>赈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>灾</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>药</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>材已</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>采办完备</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>次除了惠民</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>药</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>局，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>还</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>要各医</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>馆药铺</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>配合</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>诊治病患、发放药材</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>一会儿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>诸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>位就去</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>库</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>房画押</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>登记</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>明日起官府会张贴榜文，通知百姓就近领取药材。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>东</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>璧回来啦，什么事儿啊，一大早就被叫去了？</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
       <t>几日我去菜市街</t>
     </r>
     <r>
@@ -398,7 +1029,7 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>菜得</t>
+      <t>菜的</t>
     </r>
     <r>
       <rPr>
@@ -433,638 +1064,7 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>陈皮，跟我去后院收拾收拾库房，一会儿药材就要送来了，得赶紧腾出地方。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>陈皮</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>知州有请</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>好</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>嘞</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>一会儿</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>诸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>位就去</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>库</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>房画押</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>登记</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>，明日起官府会</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>发放榜文通知百姓就近领取药材。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>浙江省淳安建德两</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>县</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>突发水灾，周边各地已有瘟疫出现，朝廷为防止疫情扩散，特令周边州府发放赈灾药材。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>好的好的。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>朝廷</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>调拨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>了</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>赈</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>灾</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>药</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>材，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>这</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>次不光惠民</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>药</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>局，咱</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>们这</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>些医</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>馆药铺</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>也要一起帮忙</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>发</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>放。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>东</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>璧回来了啦，什么事儿啊一大早就被叫去了？</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>李大夫您在这画押，上面催得紧，我们赶着出货呢。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>昨日，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>赈</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>灾</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>药</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>材已</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>采办完备</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>这</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>次除了惠民</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>药</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>局，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>还</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>要各医</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>馆药铺</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>配合</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>诊治发放</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei UI"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>09</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>008_02</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>res://Assets/Background/0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>09</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>/0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>09</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>_01.png</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>res://Assets/Background/0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>09</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>/0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>09</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>_0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>.png</t>
-    </r>
+    <t>李大夫您在这画押，上面催得紧，我们赶着发运呢。</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1614,10 +1614,10 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>19</v>
@@ -1631,9 +1631,11 @@
       <c r="F2" s="1">
         <v>5</v>
       </c>
-      <c r="G2" s="1"/>
+      <c r="G2" s="1">
+        <v>107</v>
+      </c>
       <c r="H2" s="17" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -1819,7 +1821,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="8"/>
       <c r="G4" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>36</v>
@@ -1842,7 +1844,7 @@
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
@@ -1884,7 +1886,7 @@
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
@@ -1903,7 +1905,7 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="H8" s="19" t="s">
         <v>40</v>
@@ -1928,7 +1930,7 @@
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="20" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
@@ -1950,12 +1952,12 @@
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>6</v>
@@ -1972,12 +1974,12 @@
         <v>29</v>
       </c>
       <c r="H11" s="19" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>6</v>
@@ -1992,12 +1994,12 @@
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>6</v>
@@ -2012,12 +2014,12 @@
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="19" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>6</v>
@@ -2032,18 +2034,18 @@
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>34</v>
@@ -2052,7 +2054,7 @@
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">

--- a/DataTables/DetailText/剧情/009知州有请.xlsx
+++ b/DataTables/DetailText/剧情/009知州有请.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61BD7E42-AF12-47C1-8C54-5975ED13382A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5F0DB19-A45E-44A1-B339-771D4DAD8878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="59">
   <si>
     <t>StoryID</t>
   </si>
@@ -214,10 +214,6 @@
   </si>
   <si>
     <t>杨善泉</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>hide</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -1072,11 +1068,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1090,7 +1086,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1111,7 +1107,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1263,7 +1259,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1542,27 +1538,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.86328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -1612,12 +1608,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16">
       <c r="A2" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>19</v>
@@ -1635,7 +1631,7 @@
         <v>107</v>
       </c>
       <c r="H2" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -1650,65 +1646,65 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16">
       <c r="C3" s="10"/>
       <c r="H3" s="14"/>
       <c r="L3" s="18"/>
       <c r="O3" s="11"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16">
       <c r="C4" s="10"/>
       <c r="H4" s="14"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16">
       <c r="C5" s="10"/>
       <c r="H5" s="14"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16">
       <c r="C6" s="10"/>
       <c r="H6" s="14"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16">
       <c r="C7" s="10"/>
       <c r="H7" s="14"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:16">
       <c r="H8" s="14"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:16">
       <c r="H9" s="14"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:16">
       <c r="H10" s="14"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:16">
       <c r="H11" s="14"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:16">
       <c r="H12" s="14"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:16">
       <c r="H13" s="14"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:16">
       <c r="H14" s="14"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:16">
       <c r="H15" s="14"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:16">
       <c r="H16" s="14"/>
     </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="8:8">
       <c r="H17" s="14"/>
     </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="8:8">
       <c r="H18" s="14"/>
     </row>
-    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="8:8">
       <c r="H19" s="14"/>
     </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="8:8">
       <c r="H20" s="14"/>
     </row>
   </sheetData>
@@ -1720,20 +1716,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="93" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -1759,7 +1755,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1773,9 +1769,7 @@
         <v>8</v>
       </c>
       <c r="E2" s="2"/>
-      <c r="F2" s="8" t="s">
-        <v>38</v>
-      </c>
+      <c r="F2" s="8"/>
       <c r="G2" s="2" t="s">
         <v>29</v>
       </c>
@@ -1783,7 +1777,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1797,15 +1791,13 @@
         <v>9</v>
       </c>
       <c r="E3" s="2"/>
-      <c r="F3" s="8" t="s">
-        <v>38</v>
-      </c>
+      <c r="F3" s="8"/>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1821,13 +1813,13 @@
       <c r="E4" s="2"/>
       <c r="F4" s="8"/>
       <c r="G4" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" ht="33">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1844,10 +1836,10 @@
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1864,10 +1856,10 @@
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1881,15 +1873,13 @@
         <v>34</v>
       </c>
       <c r="E7" s="3"/>
-      <c r="F7" s="8" t="s">
-        <v>38</v>
-      </c>
+      <c r="F7" s="8"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1900,18 +1890,18 @@
         <v>37</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H8" s="19" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1925,15 +1915,13 @@
         <v>8</v>
       </c>
       <c r="E9" s="3"/>
-      <c r="F9" s="8" t="s">
-        <v>38</v>
-      </c>
+      <c r="F9" s="8"/>
       <c r="G9" s="3"/>
       <c r="H9" s="20" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1944,18 +1932,16 @@
         <v>31</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E10" s="3"/>
-      <c r="F10" s="8" t="s">
-        <v>38</v>
-      </c>
+      <c r="F10" s="8"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1963,7 +1949,7 @@
         <v>6</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>34</v>
@@ -1974,10 +1960,10 @@
         <v>29</v>
       </c>
       <c r="H11" s="19" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1985,7 +1971,7 @@
         <v>6</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>8</v>
@@ -1994,10 +1980,10 @@
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -2005,7 +1991,7 @@
         <v>6</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>9</v>
@@ -2014,10 +2000,10 @@
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="19" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -2025,7 +2011,7 @@
         <v>6</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>8</v>
@@ -2034,10 +2020,10 @@
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -2045,7 +2031,7 @@
         <v>6</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>34</v>
@@ -2054,10 +2040,10 @@
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="3"/>
@@ -2067,7 +2053,7 @@
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="3"/>
@@ -2077,7 +2063,7 @@
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="3"/>
@@ -2087,7 +2073,7 @@
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="3"/>
@@ -2097,7 +2083,7 @@
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="3"/>

--- a/DataTables/DetailText/剧情/009知州有请.xlsx
+++ b/DataTables/DetailText/剧情/009知州有请.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5F0DB19-A45E-44A1-B339-771D4DAD8878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4B9DC6D-D836-4945-B01F-D3A95E936B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -1068,11 +1068,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1086,7 +1086,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1107,7 +1107,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1259,7 +1259,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1538,27 +1538,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.86328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -1608,7 +1608,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
         <v>50</v>
       </c>
@@ -1646,65 +1646,65 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C3" s="10"/>
       <c r="H3" s="14"/>
       <c r="L3" s="18"/>
       <c r="O3" s="11"/>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C4" s="10"/>
       <c r="H4" s="14"/>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C5" s="10"/>
       <c r="H5" s="14"/>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C6" s="10"/>
       <c r="H6" s="14"/>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C7" s="10"/>
       <c r="H7" s="14"/>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H8" s="14"/>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H9" s="14"/>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H10" s="14"/>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H11" s="14"/>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H12" s="14"/>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H13" s="14"/>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H14" s="14"/>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H15" s="14"/>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H16" s="14"/>
     </row>
-    <row r="17" spans="8:8">
+    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H17" s="14"/>
     </row>
-    <row r="18" spans="8:8">
+    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H18" s="14"/>
     </row>
-    <row r="19" spans="8:8">
+    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H19" s="14"/>
     </row>
-    <row r="20" spans="8:8">
+    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H20" s="14"/>
     </row>
   </sheetData>
@@ -1716,20 +1716,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="93" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -1755,7 +1755,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1777,7 +1777,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1797,7 +1797,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1819,7 +1819,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="33">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1839,7 +1839,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1859,7 +1859,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1879,7 +1879,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1901,7 +1901,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1912,7 +1912,7 @@
         <v>37</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="8"/>
@@ -1921,7 +1921,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1932,7 +1932,7 @@
         <v>31</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="8"/>
@@ -1941,7 +1941,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1963,7 +1963,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1983,7 +1983,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -2003,7 +2003,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -2023,7 +2023,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -2043,7 +2043,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="3"/>
@@ -2053,7 +2053,7 @@
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="3"/>
@@ -2063,7 +2063,7 @@
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="3"/>
@@ -2073,7 +2073,7 @@
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="3"/>
@@ -2083,7 +2083,7 @@
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="3"/>

--- a/DataTables/DetailText/剧情/009知州有请.xlsx
+++ b/DataTables/DetailText/剧情/009知州有请.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4B9DC6D-D836-4945-B01F-D3A95E936B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50D36584-3632-432E-AB83-1C58661AF772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="60">
   <si>
     <t>StoryID</t>
   </si>
@@ -1061,6 +1061,10 @@
   </si>
   <si>
     <t>李大夫您在这画押，上面催得紧，我们赶着发运呢。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>鸡子黄</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1201,7 +1205,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1256,6 +1260,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1627,13 +1634,13 @@
       <c r="F2" s="1">
         <v>5</v>
       </c>
-      <c r="G2" s="1">
-        <v>107</v>
-      </c>
+      <c r="G2" s="1"/>
       <c r="H2" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="I2" s="1"/>
+      <c r="I2" s="21" t="s">
+        <v>59</v>
+      </c>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
       <c r="L2" s="2"/>

--- a/DataTables/DetailText/剧情/009知州有请.xlsx
+++ b/DataTables/DetailText/剧情/009知州有请.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50D36584-3632-432E-AB83-1C58661AF772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39364807-7281-4C96-B775-793BF4C2F79A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4403" yWindow="2512" windowWidth="21599" windowHeight="11423" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,26 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="60">
-  <si>
-    <t>StoryID</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="63">
   <si>
     <t>LineIndex</t>
   </si>
@@ -80,66 +66,15 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>StoryName</t>
-  </si>
-  <si>
-    <t>TriggerType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TriggerScene</t>
-  </si>
-  <si>
-    <t>NpcID</t>
-  </si>
-  <si>
     <t>PlayOnce</t>
   </si>
   <si>
-    <t>ReturnScene</t>
-  </si>
-  <si>
     <t>SortIndex</t>
   </si>
   <si>
-    <t>scene_enter</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>clinic</t>
   </si>
   <si>
-    <t>ClinicNpcPortraitPath</t>
-  </si>
-  <si>
-    <t>TriggerStoryID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TriggerDay</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Reputation</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Experience</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerReputation</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerEntryId</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Disease</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>current_scene</t>
   </si>
   <si>
@@ -1066,17 +1001,102 @@
   <si>
     <t>鸡子黄</t>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>剧情ID</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>剧情名</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发场景</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发天数</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <r>
+      <t>金</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>钱判定</t>
+    </r>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发金钱</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>名望判定</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发名望</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发条目</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发剧情ID</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发治疗结果</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>播放后</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>人物ID</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>疾病</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>人物立绘路径</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>奖励金钱</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>奖励名望</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>奖励心得</t>
+    <phoneticPr fontId="10"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1090,7 +1110,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1111,20 +1131,12 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Noto Sans JP"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Noto Sans JP"/>
@@ -1145,8 +1157,30 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Noto Sans JP"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1161,20 +1195,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF92D050"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF200"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1205,7 +1241,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1231,24 +1267,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1264,9 +1289,40 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1544,178 +1600,205 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:T20"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.9296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.06640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.06640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6" t="s">
+    <row r="1" spans="1:20" s="24" customFormat="1">
+      <c r="A1" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="F1" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="I1" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="K1" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="L1" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="M1" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="N1" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="O1" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="P1" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q1" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="R1" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="S1" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="T1" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="6" t="s">
+    </row>
+    <row r="2" spans="1:20" s="24" customFormat="1">
+      <c r="A2" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F1" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="H1" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="I1" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="L1" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M1" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="N1" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="O1" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="P1" s="16" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A2" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="1">
+      <c r="D2" s="1">
         <v>5</v>
       </c>
-      <c r="G2" s="1"/>
-      <c r="H2" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="I2" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="1" t="b">
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="25"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="26"/>
+      <c r="R2" s="27"/>
+      <c r="S2" s="27" t="b">
         <v>1</v>
       </c>
-      <c r="P2" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C3" s="10"/>
-      <c r="H3" s="14"/>
-      <c r="L3" s="18"/>
-      <c r="O3" s="11"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C4" s="10"/>
-      <c r="H4" s="14"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C5" s="10"/>
-      <c r="H5" s="14"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C6" s="10"/>
-      <c r="H6" s="14"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C7" s="10"/>
-      <c r="H7" s="14"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H8" s="14"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H9" s="14"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H10" s="14"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H11" s="14"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H12" s="14"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H13" s="14"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H14" s="14"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H15" s="14"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H16" s="14"/>
-    </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H17" s="14"/>
-    </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H18" s="14"/>
-    </row>
-    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H19" s="14"/>
-    </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H20" s="14"/>
+      <c r="T2" s="27"/>
+    </row>
+    <row r="3" spans="1:20">
+      <c r="C3" s="9"/>
+      <c r="H3" s="11"/>
+      <c r="L3" s="13"/>
+      <c r="O3" s="10"/>
+    </row>
+    <row r="4" spans="1:20" ht="18.75">
+      <c r="C4" s="9"/>
+      <c r="H4" s="11"/>
+    </row>
+    <row r="5" spans="1:20" ht="18.75">
+      <c r="C5" s="9"/>
+      <c r="H5" s="11"/>
+    </row>
+    <row r="6" spans="1:20" ht="18.75">
+      <c r="C6" s="9"/>
+      <c r="H6" s="11"/>
+    </row>
+    <row r="7" spans="1:20" ht="18.75">
+      <c r="C7" s="9"/>
+      <c r="H7" s="11"/>
+    </row>
+    <row r="8" spans="1:20" ht="18.75">
+      <c r="H8" s="11"/>
+    </row>
+    <row r="9" spans="1:20" ht="18.75">
+      <c r="H9" s="11"/>
+    </row>
+    <row r="10" spans="1:20" ht="18.75">
+      <c r="H10" s="11"/>
+    </row>
+    <row r="11" spans="1:20" ht="18.75">
+      <c r="H11" s="11"/>
+    </row>
+    <row r="12" spans="1:20" ht="18.75">
+      <c r="H12" s="11"/>
+    </row>
+    <row r="13" spans="1:20" ht="18.75">
+      <c r="H13" s="11"/>
+    </row>
+    <row r="14" spans="1:20" ht="18.75">
+      <c r="H14" s="11"/>
+    </row>
+    <row r="15" spans="1:20" ht="18.75">
+      <c r="H15" s="11"/>
+    </row>
+    <row r="16" spans="1:20" ht="18.75">
+      <c r="H16" s="11"/>
+    </row>
+    <row r="17" spans="8:8" ht="18.75">
+      <c r="H17" s="11"/>
+    </row>
+    <row r="18" spans="8:8" ht="18.75">
+      <c r="H18" s="11"/>
+    </row>
+    <row r="19" spans="8:8" ht="18.75">
+      <c r="H19" s="11"/>
+    </row>
+    <row r="20" spans="8:8">
+      <c r="H20" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
+  <dataValidations count="5">
+    <dataValidation type="list" sqref="C2" xr:uid="{7242AD4A-13C7-4553-8C97-7C34AF89B3A0}">
+      <formula1>"clinic,night,night_end"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="E2 G2" xr:uid="{D43E5EB9-5E30-43E8-8819-AF269D9F5AD3}">
+      <formula1>"≥,≤"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="L2" xr:uid="{5D92FE42-6F0E-4C77-9B74-BD98D225E10B}">
+      <formula1>"clinic,night,end_game"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="S2" xr:uid="{A1D1A2B5-14C2-4A24-A88D-0BBBBE87C205}">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="K2" xr:uid="{3E884E11-9498-4FCB-BDCD-281833279D8D}">
+      <formula1>"cured,failed"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1723,334 +1806,334 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="93" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="8"/>
       <c r="G2" s="2" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="8"/>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="8"/>
       <c r="G4" s="2" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="33">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="8"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H8" s="19" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+      <c r="H8" s="14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="8"/>
       <c r="G9" s="3"/>
-      <c r="H9" s="20" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H9" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="8"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H11" s="19" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+        <v>14</v>
+      </c>
+      <c r="H11" s="14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="1">
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="1">
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
-      <c r="H13" s="19" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H13" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="1">
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="1">
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="3"/>
@@ -2060,7 +2143,7 @@
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="3"/>
@@ -2070,7 +2153,7 @@
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="3"/>
@@ -2080,7 +2163,7 @@
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="3"/>
@@ -2090,7 +2173,7 @@
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="3"/>

--- a/DataTables/DetailText/剧情/009知州有请.xlsx
+++ b/DataTables/DetailText/剧情/009知州有请.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39364807-7281-4C96-B775-793BF4C2F79A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8FEC92B-0D11-4324-946D-FF3AC14D42FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4403" yWindow="2512" windowWidth="21599" windowHeight="11423" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19740" yWindow="5400" windowWidth="16035" windowHeight="8025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,12 +21,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="64">
   <si>
     <t>LineIndex</t>
   </si>
@@ -1085,6 +1096,10 @@
   </si>
   <si>
     <t>奖励心得</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>Music</t>
     <phoneticPr fontId="10"/>
   </si>
 </sst>
@@ -1096,7 +1111,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1110,7 +1125,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1131,7 +1146,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1241,7 +1256,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1320,9 +1335,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1601,25 +1619,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="7.1328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="7" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.9296875" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.06640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.1328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.06640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="24" customFormat="1">
+    <row r="1" spans="1:20" s="24" customFormat="1" ht="18">
       <c r="A1" s="17" t="s">
         <v>45</v>
       </c>
@@ -1681,7 +1699,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="24" customFormat="1">
+    <row r="2" spans="1:20" s="24" customFormat="1" ht="18">
       <c r="A2" s="5" t="s">
         <v>35</v>
       </c>
@@ -1725,56 +1743,56 @@
       <c r="L3" s="13"/>
       <c r="O3" s="10"/>
     </row>
-    <row r="4" spans="1:20" ht="18.75">
+    <row r="4" spans="1:20">
       <c r="C4" s="9"/>
       <c r="H4" s="11"/>
     </row>
-    <row r="5" spans="1:20" ht="18.75">
+    <row r="5" spans="1:20">
       <c r="C5" s="9"/>
       <c r="H5" s="11"/>
     </row>
-    <row r="6" spans="1:20" ht="18.75">
+    <row r="6" spans="1:20">
       <c r="C6" s="9"/>
       <c r="H6" s="11"/>
     </row>
-    <row r="7" spans="1:20" ht="18.75">
+    <row r="7" spans="1:20">
       <c r="C7" s="9"/>
       <c r="H7" s="11"/>
     </row>
-    <row r="8" spans="1:20" ht="18.75">
+    <row r="8" spans="1:20">
       <c r="H8" s="11"/>
     </row>
-    <row r="9" spans="1:20" ht="18.75">
+    <row r="9" spans="1:20">
       <c r="H9" s="11"/>
     </row>
-    <row r="10" spans="1:20" ht="18.75">
+    <row r="10" spans="1:20">
       <c r="H10" s="11"/>
     </row>
-    <row r="11" spans="1:20" ht="18.75">
+    <row r="11" spans="1:20">
       <c r="H11" s="11"/>
     </row>
-    <row r="12" spans="1:20" ht="18.75">
+    <row r="12" spans="1:20">
       <c r="H12" s="11"/>
     </row>
-    <row r="13" spans="1:20" ht="18.75">
+    <row r="13" spans="1:20">
       <c r="H13" s="11"/>
     </row>
-    <row r="14" spans="1:20" ht="18.75">
+    <row r="14" spans="1:20">
       <c r="H14" s="11"/>
     </row>
-    <row r="15" spans="1:20" ht="18.75">
+    <row r="15" spans="1:20">
       <c r="H15" s="11"/>
     </row>
-    <row r="16" spans="1:20" ht="18.75">
+    <row r="16" spans="1:20">
       <c r="H16" s="11"/>
     </row>
-    <row r="17" spans="8:8" ht="18.75">
+    <row r="17" spans="8:8">
       <c r="H17" s="11"/>
     </row>
-    <row r="18" spans="8:8" ht="18.75">
+    <row r="18" spans="8:8">
       <c r="H18" s="11"/>
     </row>
-    <row r="19" spans="8:8" ht="18.75">
+    <row r="19" spans="8:8">
       <c r="H19" s="11"/>
     </row>
     <row r="20" spans="8:8">
@@ -1805,21 +1823,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="93" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1844,8 +1862,11 @@
       <c r="H1" s="6" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="28" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1866,8 +1887,9 @@
       <c r="H2" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1886,8 +1908,9 @@
       <c r="H3" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1908,8 +1931,9 @@
       <c r="H4" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="33">
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1928,8 +1952,9 @@
       <c r="H5" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1948,8 +1973,9 @@
       <c r="H6" s="1" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1968,8 +1994,9 @@
       <c r="H7" s="3" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1990,8 +2017,9 @@
       <c r="H8" s="14" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="I8" s="3"/>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -2010,8 +2038,9 @@
       <c r="H9" s="15" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="I9" s="3"/>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -2030,8 +2059,9 @@
       <c r="H10" s="3" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="I10" s="3"/>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -2052,8 +2082,9 @@
       <c r="H11" s="14" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="I11" s="3"/>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -2072,8 +2103,9 @@
       <c r="H12" s="3" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="I12" s="3"/>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -2092,8 +2124,9 @@
       <c r="H13" s="14" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="14" spans="1:8">
+      <c r="I13" s="3"/>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -2112,8 +2145,9 @@
       <c r="H14" s="3" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="15" spans="1:8">
+      <c r="I14" s="3"/>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -2132,8 +2166,9 @@
       <c r="H15" s="3" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="16" spans="1:8">
+      <c r="I15" s="3"/>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="3"/>
@@ -2142,8 +2177,9 @@
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
-    </row>
-    <row r="17" spans="1:8">
+      <c r="I16" s="3"/>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="3"/>
@@ -2152,8 +2188,9 @@
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
-    </row>
-    <row r="18" spans="1:8">
+      <c r="I17" s="3"/>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="3"/>
@@ -2162,8 +2199,9 @@
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
-    </row>
-    <row r="19" spans="1:8">
+      <c r="I18" s="3"/>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="3"/>
@@ -2172,8 +2210,9 @@
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
-    </row>
-    <row r="20" spans="1:8">
+      <c r="I19" s="3"/>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="3"/>
@@ -2182,6 +2221,7 @@
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/DataTables/DetailText/剧情/009知州有请.xlsx
+++ b/DataTables/DetailText/剧情/009知州有请.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8FEC92B-0D11-4324-946D-FF3AC14D42FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84EB2C1D-A438-484E-B531-985F720B8CEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19740" yWindow="5400" windowWidth="16035" windowHeight="8025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -552,10 +552,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>008_02</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <r>
       <t>res://Assets/Background/0</t>
     </r>
@@ -1007,10 +1003,6 @@
   </si>
   <si>
     <t>李大夫您在这画押，上面催得紧，我们赶着发运呢。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>鸡子黄</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -1101,6 +1093,14 @@
   <si>
     <t>Music</t>
     <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>026_02</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>鸡子黄</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -1639,58 +1639,58 @@
   <sheetData>
     <row r="1" spans="1:20" s="24" customFormat="1" ht="18">
       <c r="A1" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="D1" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="E1" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="F1" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="G1" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="F1" s="20" t="s">
+      <c r="H1" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="G1" s="20" t="s">
+      <c r="I1" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="H1" s="20" t="s">
+      <c r="J1" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="I1" s="20" t="s">
+      <c r="K1" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="20" t="s">
+      <c r="L1" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="K1" s="20" t="s">
+      <c r="M1" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="L1" s="21" t="s">
+      <c r="N1" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="M1" s="22" t="s">
+      <c r="O1" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="N1" s="22" t="s">
+      <c r="P1" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="O1" s="22" t="s">
+      <c r="Q1" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="P1" s="22" t="s">
+      <c r="R1" s="22" t="s">
         <v>60</v>
-      </c>
-      <c r="Q1" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="R1" s="22" t="s">
-        <v>62</v>
       </c>
       <c r="S1" s="23" t="s">
         <v>11</v>
@@ -1717,10 +1717,10 @@
       <c r="G2" s="26"/>
       <c r="H2" s="26"/>
       <c r="I2" s="16" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="J2" s="12" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="K2" s="26"/>
       <c r="L2" s="26" t="s">
@@ -1863,7 +1863,7 @@
         <v>4</v>
       </c>
       <c r="I1" s="28" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1926,7 +1926,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="8"/>
       <c r="G4" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>21</v>
@@ -1971,7 +1971,7 @@
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I6" s="1"/>
     </row>
@@ -1992,7 +1992,7 @@
       <c r="F7" s="8"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I7" s="3"/>
     </row>
@@ -2012,7 +2012,7 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H8" s="14" t="s">
         <v>24</v>
@@ -2036,7 +2036,7 @@
       <c r="F9" s="8"/>
       <c r="G9" s="3"/>
       <c r="H9" s="15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I9" s="3"/>
     </row>
@@ -2080,7 +2080,7 @@
         <v>14</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I11" s="3"/>
     </row>
@@ -2122,7 +2122,7 @@
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I13" s="3"/>
     </row>
